--- a/backend/signal_logs/signals_2026-08-05.xlsx
+++ b/backend/signal_logs/signals_2026-08-05.xlsx
@@ -885,6 +885,11 @@
           <t>NSE:DIXON26AUG14250CE</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Closed up ~444.15 (+6.8% from entry)</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>2026-08-05 16:19:03</t>
@@ -979,6 +984,16 @@
           <t>NSE:HEROMOTOCO26AUG5600CE</t>
         </is>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-05 10:20:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>2026-08-05 14:29:29</t>
@@ -1073,6 +1088,11 @@
           <t>NSE:AUROPHARMA26AUG1620CE</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Closed down ~51.0 (-4.5% from entry)</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
           <t>2026-08-05 10:22:21</t>
@@ -1162,6 +1182,11 @@
           <t>NSE:LODHA26AUG1260CE</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Closed up ~37.35 (+2.5% from entry)</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>2026-08-05 11:03:53</t>
@@ -1256,6 +1281,11 @@
           <t>NSE:GODREJPROP26AUG2140CE</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Closed down ~54.55 (-15.8% from entry)</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
           <t>2026-08-05 13:14:57</t>
@@ -1350,6 +1380,11 @@
           <t>NSE:AUROPHARMA26AUG1620CE</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Closed down ~52.0 (-4.5% from entry)</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
           <t>2026-08-05 11:51:14</t>
@@ -1444,6 +1479,11 @@
           <t>NSE:MARICO26AUG850CE</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Closed up ~21.55 (+2.6% from entry)</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
           <t>2026-08-05 16:19:02</t>
@@ -1642,6 +1682,11 @@
           <t>NSE:ICICIGI26AUG1680PE</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Closed up ~38.0 (+1.9% from entry)</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
           <t>2026-08-05 14:36:20</t>
@@ -1736,6 +1781,11 @@
           <t>NSE:AUROPHARMA26AUG1620CE</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Closed down ~50.85 (-2.6% from entry)</t>
+        </is>
+      </c>
       <c r="AC13" t="inlineStr">
         <is>
           <t>2026-08-05 13:42:12</t>
@@ -1830,6 +1880,11 @@
           <t>NSE:TVSMOTOR26AUG4450CE</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Closed flat ~110.0 (+0.2% from entry)</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
           <t>2026-08-05 13:53:28</t>
@@ -1924,6 +1979,11 @@
           <t>NSE:NHPC26AUG79CE</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Closed down ~1.69 (-4.0% from entry)</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
           <t>2026-08-05 16:19:02</t>
@@ -2018,6 +2078,11 @@
           <t>NSE:AUROPHARMA26AUG1620CE</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Closed flat ~54.5 (-0.1% from entry)</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
           <t>2026-08-05 14:52:13</t>
@@ -2112,6 +2177,11 @@
           <t>NSE:HEROMOTOCO26AUG5700CE</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Closed up ~160.0 (+2.4% from entry)</t>
+        </is>
+      </c>
       <c r="AC17" t="inlineStr">
         <is>
           <t>2026-08-05 16:19:03</t>
@@ -2204,6 +2274,11 @@
       <c r="W18" t="inlineStr">
         <is>
           <t>NSE:ICICIGI26AUG1680PE</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Closed up ~34.5 (+5.3% from entry)</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
